--- a/SAR/Mercedes/TP4 Filtros/radiometric_uncertainty/output.xlsx
+++ b/SAR/Mercedes/TP4 Filtros/radiometric_uncertainty/output.xlsx
@@ -475,31 +475,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08804819732904434</v>
+        <v>0.08874602615833282</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01137882750481367</v>
+        <v>0.01165448129177094</v>
       </c>
       <c r="D2" t="n">
-        <v>59.87505722045898</v>
+        <v>57.98450469970703</v>
       </c>
       <c r="E2" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="F2" t="n">
-        <v>50.09</v>
+        <v>50.52</v>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>90.09999999999999</v>
+        <v>89.92</v>
       </c>
       <c r="I2" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="J2" t="n">
-        <v>95.05</v>
+        <v>95.09</v>
       </c>
     </row>
     <row r="3">
@@ -509,31 +509,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5753756761550903</v>
+        <v>0.5767802000045776</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1565760374069214</v>
+        <v>0.1662348210811615</v>
       </c>
       <c r="D3" t="n">
-        <v>13.50368881225586</v>
+        <v>12.03861999511719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="F3" t="n">
-        <v>49.84</v>
+        <v>49.94</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>89.95999999999999</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="J3" t="n">
-        <v>95.03</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="4">
@@ -543,31 +543,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005133811850100756</v>
+        <v>0.005137117113918066</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001844647340476513</v>
+        <v>0.0002145526232197881</v>
       </c>
       <c r="D4" t="n">
-        <v>774.556640625</v>
+        <v>573.2859497070312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="F4" t="n">
-        <v>51.91</v>
+        <v>49.17</v>
       </c>
       <c r="G4" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
       <c r="H4" t="n">
-        <v>90.42</v>
+        <v>90.17</v>
       </c>
       <c r="I4" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="J4" t="n">
-        <v>95.29000000000001</v>
+        <v>95.27</v>
       </c>
     </row>
   </sheetData>
